--- a/sub_pro_8_university_kenya/datasets/Kenya Universities List.xlsx
+++ b/sub_pro_8_university_kenya/datasets/Kenya Universities List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\kenya_in_numbers_1\sub_pro_8_university_kenya\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C411CCD-B5C0-4525-8A3D-33A2B283EFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DD14B3-2C52-46F2-B4B4-72CD87A3FD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="434" xr2:uid="{61A5876C-E1AA-4F3A-91B0-BFF9EA50D7A2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="206">
   <si>
     <t>Kenya Medical Research Institute</t>
   </si>
@@ -282,9 +282,6 @@
     <t>Kamagambo University College</t>
   </si>
   <si>
-    <t>University Name</t>
-  </si>
-  <si>
     <t>Kiriri Women's University of Science and Tech</t>
   </si>
   <si>
@@ -640,6 +637,12 @@
   </si>
   <si>
     <t>-1.6900392485595832, 37.172800824699245</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Schools and Faculties</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1010,7 @@
     <col min="3" max="3" width="16.26953125" customWidth="1"/>
     <col min="4" max="4" width="21.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1015,18 +1018,20 @@
         <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
@@ -1039,10 +1044,10 @@
         <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1056,10 +1061,10 @@
         <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1073,10 +1078,10 @@
         <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1090,10 +1095,10 @@
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1107,10 +1112,10 @@
         <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1124,10 +1129,10 @@
         <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1141,10 +1146,10 @@
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1158,10 +1163,10 @@
         <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1175,10 +1180,10 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1192,10 +1197,10 @@
         <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1209,10 +1214,10 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1226,10 +1231,10 @@
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1243,10 +1248,10 @@
         <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1260,10 +1265,10 @@
         <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1277,10 +1282,10 @@
         <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1294,10 +1299,10 @@
         <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1311,10 +1316,10 @@
         <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1328,10 +1333,10 @@
         <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1345,10 +1350,10 @@
         <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1362,10 +1367,10 @@
         <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1379,10 +1384,10 @@
         <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -1396,10 +1401,10 @@
         <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1413,10 +1418,10 @@
         <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -1430,10 +1435,10 @@
         <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1447,10 +1452,10 @@
         <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1464,10 +1469,10 @@
         <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1481,10 +1486,10 @@
         <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -1492,16 +1497,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
         <v>86</v>
       </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
-      </c>
       <c r="E29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -1515,10 +1520,10 @@
         <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1532,10 +1537,10 @@
         <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -1549,10 +1554,10 @@
         <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -1566,10 +1571,10 @@
         <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1583,10 +1588,10 @@
         <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1600,10 +1605,10 @@
         <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1617,10 +1622,10 @@
         <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -1634,10 +1639,10 @@
         <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1651,10 +1656,10 @@
         <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1668,10 +1673,10 @@
         <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1685,10 +1690,10 @@
         <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -1702,10 +1707,10 @@
         <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -1719,10 +1724,10 @@
         <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1736,10 +1741,10 @@
         <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1753,10 +1758,10 @@
         <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -1770,10 +1775,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -1787,10 +1792,10 @@
         <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -1804,10 +1809,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -1821,10 +1826,10 @@
         <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -1838,10 +1843,10 @@
         <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E49" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -1855,10 +1860,10 @@
         <v>81</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -1872,10 +1877,10 @@
         <v>82</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -1889,10 +1894,10 @@
         <v>82</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -1906,10 +1911,10 @@
         <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -1923,10 +1928,10 @@
         <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -1940,10 +1945,10 @@
         <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -1957,10 +1962,10 @@
         <v>82</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -1974,10 +1979,10 @@
         <v>82</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -1991,10 +1996,10 @@
         <v>82</v>
       </c>
       <c r="D58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -2008,10 +2013,10 @@
         <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -2025,10 +2030,10 @@
         <v>81</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -2042,10 +2047,10 @@
         <v>82</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -2059,10 +2064,10 @@
         <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E62" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -2076,10 +2081,10 @@
         <v>82</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -2093,10 +2098,10 @@
         <v>81</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E64" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -2110,10 +2115,10 @@
         <v>82</v>
       </c>
       <c r="D65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -2127,10 +2132,10 @@
         <v>82</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E66" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -2144,10 +2149,10 @@
         <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2161,10 +2166,10 @@
         <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -2178,10 +2183,10 @@
         <v>81</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -2189,16 +2194,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>194</v>
+      </c>
+      <c r="C70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" t="s">
+        <v>86</v>
+      </c>
+      <c r="E70" t="s">
         <v>195</v>
-      </c>
-      <c r="C70" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" t="s">
-        <v>87</v>
-      </c>
-      <c r="E70" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -2212,10 +2217,10 @@
         <v>82</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -2229,10 +2234,10 @@
         <v>82</v>
       </c>
       <c r="D72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -2246,10 +2251,10 @@
         <v>81</v>
       </c>
       <c r="D73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -2263,10 +2268,10 @@
         <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -2280,10 +2285,10 @@
         <v>81</v>
       </c>
       <c r="D75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
@@ -2297,10 +2302,10 @@
         <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -2314,10 +2319,10 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E77" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -2331,10 +2336,10 @@
         <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E78" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -2348,10 +2353,10 @@
         <v>82</v>
       </c>
       <c r="D79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
@@ -2365,10 +2370,10 @@
         <v>82</v>
       </c>
       <c r="D80" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -2382,10 +2387,10 @@
         <v>82</v>
       </c>
       <c r="D81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
@@ -2399,10 +2404,10 @@
         <v>81</v>
       </c>
       <c r="D82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E82" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -2416,10 +2421,10 @@
         <v>82</v>
       </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E83" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
@@ -2433,10 +2438,10 @@
         <v>82</v>
       </c>
       <c r="D84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
